--- a/diagnostics_code/aortic_valve_disease_codes_reviewed.xlsx
+++ b/diagnostics_code/aortic_valve_disease_codes_reviewed.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29728"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10118"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/orms0426/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/orms0426/Documents/GitHub/HERON-UK-02-002-CVDValveReplacement/diagnostics_code/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{111C7ED3-6677-423E-991C-65E558326FE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB304DEE-A553-4A45-86B5-40858883ED46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="680" windowWidth="26520" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1480" yWindow="680" windowWidth="29960" windowHeight="20340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="codes_for_review" sheetId="1" r:id="rId1"/>
@@ -1586,7 +1586,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1933,19 +1933,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H279"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="116.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="116.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.33203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="16" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1">
+    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1971,7 +1971,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>259123</v>
       </c>
@@ -1994,10 +1994,10 @@
         <v>13</v>
       </c>
       <c r="H2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>313007</v>
       </c>
@@ -2023,7 +2023,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>313221</v>
       </c>
@@ -2049,7 +2049,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>314054</v>
       </c>
@@ -2075,7 +2075,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>314368</v>
       </c>
@@ -2101,7 +2101,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>314457</v>
       </c>
@@ -2127,7 +2127,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>315282</v>
       </c>
@@ -2153,7 +2153,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>315564</v>
       </c>
@@ -2179,7 +2179,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>317890</v>
       </c>
@@ -2205,7 +2205,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>318689</v>
       </c>
@@ -2231,7 +2231,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>318776</v>
       </c>
@@ -2257,7 +2257,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>320115</v>
       </c>
@@ -2283,7 +2283,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>320416</v>
       </c>
@@ -2309,7 +2309,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>320429</v>
       </c>
@@ -2335,7 +2335,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>321041</v>
       </c>
@@ -2361,7 +2361,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:8">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>321107</v>
       </c>
@@ -2387,7 +2387,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:8">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>439834</v>
       </c>
@@ -2413,7 +2413,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:8">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>443962</v>
       </c>
@@ -2439,7 +2439,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>600625</v>
       </c>
@@ -2462,10 +2462,10 @@
         <v>13</v>
       </c>
       <c r="H20" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>604345</v>
       </c>
@@ -2491,7 +2491,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:8">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>605551</v>
       </c>
@@ -2517,7 +2517,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="23" spans="1:8">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>605552</v>
       </c>
@@ -2543,7 +2543,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="24" spans="1:8">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>605778</v>
       </c>
@@ -2569,7 +2569,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="25" spans="1:8">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>605897</v>
       </c>
@@ -2595,7 +2595,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="26" spans="1:8">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>606038</v>
       </c>
@@ -2621,7 +2621,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="27" spans="1:8">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>606159</v>
       </c>
@@ -2647,7 +2647,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="28" spans="1:8">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>607641</v>
       </c>
@@ -2673,7 +2673,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="29" spans="1:8">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>618992</v>
       </c>
@@ -2699,7 +2699,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="30" spans="1:8">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>618994</v>
       </c>
@@ -2725,7 +2725,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="31" spans="1:8">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>619135</v>
       </c>
@@ -2751,7 +2751,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="32" spans="1:8">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>619141</v>
       </c>
@@ -2777,7 +2777,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="33" spans="1:8">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>1244580</v>
       </c>
@@ -2803,7 +2803,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="34" spans="1:8">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>1244581</v>
       </c>
@@ -2829,7 +2829,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="35" spans="1:8">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>3654574</v>
       </c>
@@ -2855,7 +2855,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="36" spans="1:8">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>3654575</v>
       </c>
@@ -2881,7 +2881,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="37" spans="1:8">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>3654576</v>
       </c>
@@ -2907,7 +2907,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="38" spans="1:8">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>3654726</v>
       </c>
@@ -2933,7 +2933,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="39" spans="1:8">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>3654727</v>
       </c>
@@ -2959,7 +2959,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="40" spans="1:8">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>3654728</v>
       </c>
@@ -2985,7 +2985,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="41" spans="1:8">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>3654729</v>
       </c>
@@ -3011,7 +3011,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="42" spans="1:8">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>3654730</v>
       </c>
@@ -3037,7 +3037,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="43" spans="1:8">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>3654731</v>
       </c>
@@ -3063,7 +3063,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="44" spans="1:8">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>3654795</v>
       </c>
@@ -3089,7 +3089,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="45" spans="1:8">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>3654796</v>
       </c>
@@ -3115,7 +3115,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="46" spans="1:8">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>3654797</v>
       </c>
@@ -3141,7 +3141,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="47" spans="1:8">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>3654798</v>
       </c>
@@ -3167,7 +3167,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="48" spans="1:8">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>3654799</v>
       </c>
@@ -3193,7 +3193,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="49" spans="1:8">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>3654800</v>
       </c>
@@ -3219,7 +3219,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="50" spans="1:8">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>3654940</v>
       </c>
@@ -3245,7 +3245,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="51" spans="1:8">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>3654955</v>
       </c>
@@ -3271,7 +3271,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="52" spans="1:8">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>3656075</v>
       </c>
@@ -3297,7 +3297,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="53" spans="1:8">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>3656077</v>
       </c>
@@ -3323,7 +3323,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="54" spans="1:8">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>3656079</v>
       </c>
@@ -3349,7 +3349,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="55" spans="1:8">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>3656100</v>
       </c>
@@ -3375,7 +3375,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="56" spans="1:8">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>3656127</v>
       </c>
@@ -3401,7 +3401,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="57" spans="1:8">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>3656136</v>
       </c>
@@ -3427,7 +3427,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="58" spans="1:8">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>3656142</v>
       </c>
@@ -3453,7 +3453,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="59" spans="1:8">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>4006971</v>
       </c>
@@ -3479,7 +3479,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="60" spans="1:8">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>4012483</v>
       </c>
@@ -3505,7 +3505,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="61" spans="1:8">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>4030224</v>
       </c>
@@ -3531,7 +3531,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="62" spans="1:8">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>4035467</v>
       </c>
@@ -3557,7 +3557,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="63" spans="1:8">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>4040820</v>
       </c>
@@ -3583,7 +3583,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="64" spans="1:8">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>4048213</v>
       </c>
@@ -3609,7 +3609,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="65" spans="1:8">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A65">
         <v>4058384</v>
       </c>
@@ -3635,7 +3635,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="66" spans="1:8">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>4069183</v>
       </c>
@@ -3661,7 +3661,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="67" spans="1:8">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>4081037</v>
       </c>
@@ -3687,7 +3687,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="68" spans="1:8">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>4102992</v>
       </c>
@@ -3713,7 +3713,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="69" spans="1:8">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>4103319</v>
       </c>
@@ -3739,7 +3739,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="70" spans="1:8">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>4108085</v>
       </c>
@@ -3765,7 +3765,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="71" spans="1:8">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A71">
         <v>4108164</v>
       </c>
@@ -3791,7 +3791,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="72" spans="1:8">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A72">
         <v>4108165</v>
       </c>
@@ -3817,7 +3817,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="73" spans="1:8">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A73">
         <v>4108235</v>
       </c>
@@ -3843,7 +3843,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="74" spans="1:8">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A74">
         <v>4108595</v>
       </c>
@@ -3869,7 +3869,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="75" spans="1:8">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A75">
         <v>4108596</v>
       </c>
@@ -3895,7 +3895,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="76" spans="1:8">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A76">
         <v>4108659</v>
       </c>
@@ -3921,7 +3921,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="77" spans="1:8">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A77">
         <v>4108723</v>
       </c>
@@ -3947,7 +3947,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="78" spans="1:8">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A78">
         <v>4108729</v>
       </c>
@@ -3973,7 +3973,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="79" spans="1:8">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A79">
         <v>4108730</v>
       </c>
@@ -3999,7 +3999,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="80" spans="1:8">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A80">
         <v>4108731</v>
       </c>
@@ -4025,7 +4025,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="81" spans="1:8">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A81">
         <v>4108732</v>
       </c>
@@ -4051,7 +4051,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="82" spans="1:8">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A82">
         <v>4108815</v>
       </c>
@@ -4077,7 +4077,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="83" spans="1:8">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A83">
         <v>4108819</v>
       </c>
@@ -4103,7 +4103,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="84" spans="1:8">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A84">
         <v>4109202</v>
       </c>
@@ -4129,7 +4129,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="85" spans="1:8">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A85">
         <v>4109324</v>
       </c>
@@ -4155,7 +4155,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="86" spans="1:8">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A86">
         <v>4109338</v>
       </c>
@@ -4181,7 +4181,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="87" spans="1:8">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A87">
         <v>4109340</v>
       </c>
@@ -4207,7 +4207,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="88" spans="1:8">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A88">
         <v>4109341</v>
       </c>
@@ -4233,7 +4233,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="89" spans="1:8">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A89">
         <v>4109347</v>
       </c>
@@ -4259,7 +4259,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="90" spans="1:8">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A90">
         <v>4109463</v>
       </c>
@@ -4285,7 +4285,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="91" spans="1:8">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A91">
         <v>4111098</v>
       </c>
@@ -4311,7 +4311,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="92" spans="1:8">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A92">
         <v>4111099</v>
       </c>
@@ -4337,7 +4337,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="93" spans="1:8">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A93">
         <v>4111409</v>
       </c>
@@ -4363,7 +4363,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="94" spans="1:8">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A94">
         <v>4111412</v>
       </c>
@@ -4389,7 +4389,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="95" spans="1:8">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A95">
         <v>4111414</v>
       </c>
@@ -4415,7 +4415,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="96" spans="1:8">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A96">
         <v>4111416</v>
       </c>
@@ -4441,7 +4441,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="97" spans="1:8">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A97">
         <v>4111565</v>
       </c>
@@ -4467,7 +4467,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="98" spans="1:8">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A98">
         <v>4112083</v>
       </c>
@@ -4493,7 +4493,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="99" spans="1:8">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A99">
         <v>4112091</v>
       </c>
@@ -4519,7 +4519,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="100" spans="1:8">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A100">
         <v>4112092</v>
       </c>
@@ -4545,7 +4545,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="101" spans="1:8">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A101">
         <v>4112093</v>
       </c>
@@ -4571,7 +4571,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="102" spans="1:8">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A102">
         <v>4113295</v>
       </c>
@@ -4597,7 +4597,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="103" spans="1:8">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A103">
         <v>4119463</v>
       </c>
@@ -4617,13 +4617,13 @@
         <v>12</v>
       </c>
       <c r="G103" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H103" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="104" spans="1:8">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A104">
         <v>4119589</v>
       </c>
@@ -4649,7 +4649,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="105" spans="1:8">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A105">
         <v>4119956</v>
       </c>
@@ -4669,13 +4669,13 @@
         <v>12</v>
       </c>
       <c r="G105" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H105" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="106" spans="1:8">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A106">
         <v>4119957</v>
       </c>
@@ -4701,7 +4701,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="107" spans="1:8">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A107">
         <v>4121472</v>
       </c>
@@ -4727,7 +4727,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="108" spans="1:8">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A108">
         <v>4124690</v>
       </c>
@@ -4753,7 +4753,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="109" spans="1:8">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A109">
         <v>4125004</v>
       </c>
@@ -4779,7 +4779,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="110" spans="1:8">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A110">
         <v>4133509</v>
       </c>
@@ -4805,7 +4805,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="111" spans="1:8">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A111">
         <v>4143607</v>
       </c>
@@ -4831,7 +4831,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="112" spans="1:8">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A112">
         <v>4144901</v>
       </c>
@@ -4857,7 +4857,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="113" spans="1:8">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A113">
         <v>4147787</v>
       </c>
@@ -4883,7 +4883,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="114" spans="1:8">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A114">
         <v>4152384</v>
       </c>
@@ -4909,7 +4909,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="115" spans="1:8">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A115">
         <v>4154293</v>
       </c>
@@ -4935,7 +4935,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="116" spans="1:8">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A116">
         <v>4155964</v>
       </c>
@@ -4961,7 +4961,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="117" spans="1:8">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A117">
         <v>4156119</v>
       </c>
@@ -4987,7 +4987,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="118" spans="1:8">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A118">
         <v>4161245</v>
       </c>
@@ -5013,7 +5013,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="119" spans="1:8">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A119">
         <v>4161458</v>
       </c>
@@ -5039,7 +5039,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="120" spans="1:8">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A120">
         <v>4161459</v>
       </c>
@@ -5065,7 +5065,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="121" spans="1:8">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A121">
         <v>4161975</v>
       </c>
@@ -5091,7 +5091,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="122" spans="1:8">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A122">
         <v>4172866</v>
       </c>
@@ -5117,7 +5117,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="123" spans="1:8">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A123">
         <v>4181949</v>
       </c>
@@ -5143,7 +5143,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="124" spans="1:8">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A124">
         <v>4182110</v>
       </c>
@@ -5169,7 +5169,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="125" spans="1:8">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A125">
         <v>4188554</v>
       </c>
@@ -5195,7 +5195,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="126" spans="1:8">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A126">
         <v>4189343</v>
       </c>
@@ -5221,7 +5221,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="127" spans="1:8">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A127">
         <v>4189522</v>
       </c>
@@ -5247,7 +5247,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="128" spans="1:8">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A128">
         <v>4195677</v>
       </c>
@@ -5273,7 +5273,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="129" spans="1:8">
+    <row r="129" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A129">
         <v>4195690</v>
       </c>
@@ -5296,10 +5296,10 @@
         <v>13</v>
       </c>
       <c r="H129" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="130" spans="1:8">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A130">
         <v>4197259</v>
       </c>
@@ -5325,7 +5325,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="131" spans="1:8">
+    <row r="131" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A131">
         <v>4207052</v>
       </c>
@@ -5351,7 +5351,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="132" spans="1:8">
+    <row r="132" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A132">
         <v>4215619</v>
       </c>
@@ -5377,7 +5377,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="133" spans="1:8">
+    <row r="133" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A133">
         <v>4218450</v>
       </c>
@@ -5403,7 +5403,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="134" spans="1:8">
+    <row r="134" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A134">
         <v>4219047</v>
       </c>
@@ -5429,7 +5429,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="135" spans="1:8">
+    <row r="135" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A135">
         <v>4230774</v>
       </c>
@@ -5455,7 +5455,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="136" spans="1:8">
+    <row r="136" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A136">
         <v>4231324</v>
       </c>
@@ -5481,7 +5481,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="137" spans="1:8">
+    <row r="137" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A137">
         <v>4231818</v>
       </c>
@@ -5507,7 +5507,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="138" spans="1:8">
+    <row r="138" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A138">
         <v>4237202</v>
       </c>
@@ -5533,7 +5533,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="139" spans="1:8">
+    <row r="139" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A139">
         <v>4242036</v>
       </c>
@@ -5559,7 +5559,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="140" spans="1:8">
+    <row r="140" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A140">
         <v>4244173</v>
       </c>
@@ -5585,7 +5585,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="141" spans="1:8">
+    <row r="141" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A141">
         <v>4244437</v>
       </c>
@@ -5611,7 +5611,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="142" spans="1:8">
+    <row r="142" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A142">
         <v>4244935</v>
       </c>
@@ -5637,7 +5637,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="143" spans="1:8">
+    <row r="143" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A143">
         <v>4244966</v>
       </c>
@@ -5663,7 +5663,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="144" spans="1:8">
+    <row r="144" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A144">
         <v>4245692</v>
       </c>
@@ -5689,7 +5689,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="145" spans="1:8">
+    <row r="145" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A145">
         <v>4246657</v>
       </c>
@@ -5715,7 +5715,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="146" spans="1:8">
+    <row r="146" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A146">
         <v>4246951</v>
       </c>
@@ -5741,7 +5741,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="147" spans="1:8">
+    <row r="147" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A147">
         <v>4259295</v>
       </c>
@@ -5767,7 +5767,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="148" spans="1:8">
+    <row r="148" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A148">
         <v>4298429</v>
       </c>
@@ -5793,7 +5793,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="149" spans="1:8">
+    <row r="149" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A149">
         <v>4301373</v>
       </c>
@@ -5819,7 +5819,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="150" spans="1:8">
+    <row r="150" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A150">
         <v>4304541</v>
       </c>
@@ -5845,7 +5845,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="151" spans="1:8">
+    <row r="151" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A151">
         <v>4305961</v>
       </c>
@@ -5871,7 +5871,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="152" spans="1:8">
+    <row r="152" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A152">
         <v>4312621</v>
       </c>
@@ -5897,7 +5897,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="153" spans="1:8">
+    <row r="153" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A153">
         <v>4324608</v>
       </c>
@@ -5923,7 +5923,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="154" spans="1:8">
+    <row r="154" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A154">
         <v>4324704</v>
       </c>
@@ -5949,7 +5949,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="155" spans="1:8">
+    <row r="155" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A155">
         <v>4337282</v>
       </c>
@@ -5975,7 +5975,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="156" spans="1:8">
+    <row r="156" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A156">
         <v>4353740</v>
       </c>
@@ -6001,7 +6001,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="157" spans="1:8">
+    <row r="157" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A157">
         <v>4353743</v>
       </c>
@@ -6027,7 +6027,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="158" spans="1:8">
+    <row r="158" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A158">
         <v>4353822</v>
       </c>
@@ -6053,7 +6053,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="159" spans="1:8">
+    <row r="159" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A159">
         <v>4354063</v>
       </c>
@@ -6079,7 +6079,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="160" spans="1:8">
+    <row r="160" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A160">
         <v>4354064</v>
       </c>
@@ -6105,7 +6105,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="161" spans="1:8">
+    <row r="161" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A161">
         <v>4354065</v>
       </c>
@@ -6131,7 +6131,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="162" spans="1:8">
+    <row r="162" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A162">
         <v>4354066</v>
       </c>
@@ -6157,7 +6157,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="163" spans="1:8">
+    <row r="163" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A163">
         <v>35622773</v>
       </c>
@@ -6183,7 +6183,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="164" spans="1:8">
+    <row r="164" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A164">
         <v>36674716</v>
       </c>
@@ -6209,7 +6209,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="165" spans="1:8">
+    <row r="165" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A165">
         <v>36674972</v>
       </c>
@@ -6235,7 +6235,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="166" spans="1:8">
+    <row r="166" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A166">
         <v>36684984</v>
       </c>
@@ -6261,7 +6261,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="167" spans="1:8">
+    <row r="167" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A167">
         <v>36715123</v>
       </c>
@@ -6287,7 +6287,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="168" spans="1:8">
+    <row r="168" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A168">
         <v>37163073</v>
       </c>
@@ -6313,7 +6313,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="169" spans="1:8">
+    <row r="169" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A169">
         <v>37163275</v>
       </c>
@@ -6339,7 +6339,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="170" spans="1:8">
+    <row r="170" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A170">
         <v>37165735</v>
       </c>
@@ -6365,7 +6365,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="171" spans="1:8">
+    <row r="171" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A171">
         <v>37204437</v>
       </c>
@@ -6391,7 +6391,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="172" spans="1:8">
+    <row r="172" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A172">
         <v>40482894</v>
       </c>
@@ -6417,7 +6417,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="173" spans="1:8">
+    <row r="173" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A173">
         <v>40482925</v>
       </c>
@@ -6443,7 +6443,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="174" spans="1:8">
+    <row r="174" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A174">
         <v>40483337</v>
       </c>
@@ -6469,7 +6469,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="175" spans="1:8">
+    <row r="175" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A175">
         <v>40484273</v>
       </c>
@@ -6495,7 +6495,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="176" spans="1:8">
+    <row r="176" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A176">
         <v>40484305</v>
       </c>
@@ -6521,7 +6521,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="177" spans="1:8">
+    <row r="177" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A177">
         <v>40486044</v>
       </c>
@@ -6547,7 +6547,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="178" spans="1:8">
+    <row r="178" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A178">
         <v>40486056</v>
       </c>
@@ -6573,7 +6573,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="179" spans="1:8">
+    <row r="179" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A179">
         <v>40486057</v>
       </c>
@@ -6599,7 +6599,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="180" spans="1:8">
+    <row r="180" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A180">
         <v>40486071</v>
       </c>
@@ -6625,7 +6625,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="181" spans="1:8">
+    <row r="181" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A181">
         <v>40486073</v>
       </c>
@@ -6651,7 +6651,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="182" spans="1:8">
+    <row r="182" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A182">
         <v>40486608</v>
       </c>
@@ -6677,7 +6677,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="183" spans="1:8">
+    <row r="183" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A183">
         <v>40486635</v>
       </c>
@@ -6703,7 +6703,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="184" spans="1:8">
+    <row r="184" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A184">
         <v>40487107</v>
       </c>
@@ -6729,7 +6729,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="185" spans="1:8">
+    <row r="185" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A185">
         <v>40487183</v>
       </c>
@@ -6755,7 +6755,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="186" spans="1:8">
+    <row r="186" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A186">
         <v>40487184</v>
       </c>
@@ -6781,7 +6781,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="187" spans="1:8">
+    <row r="187" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A187">
         <v>40487186</v>
       </c>
@@ -6807,7 +6807,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="188" spans="1:8">
+    <row r="188" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A188">
         <v>40487600</v>
       </c>
@@ -6833,7 +6833,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="189" spans="1:8">
+    <row r="189" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A189">
         <v>40487652</v>
       </c>
@@ -6859,7 +6859,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="190" spans="1:8">
+    <row r="190" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A190">
         <v>40487653</v>
       </c>
@@ -6885,7 +6885,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="191" spans="1:8">
+    <row r="191" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A191">
         <v>40487654</v>
       </c>
@@ -6911,7 +6911,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="192" spans="1:8">
+    <row r="192" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A192">
         <v>40487672</v>
       </c>
@@ -6937,7 +6937,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="193" spans="1:8">
+    <row r="193" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A193">
         <v>40487966</v>
       </c>
@@ -6963,7 +6963,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="194" spans="1:8">
+    <row r="194" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A194">
         <v>40487992</v>
       </c>
@@ -6989,7 +6989,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="195" spans="1:8">
+    <row r="195" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A195">
         <v>40488014</v>
       </c>
@@ -7015,7 +7015,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="196" spans="1:8">
+    <row r="196" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A196">
         <v>40488397</v>
       </c>
@@ -7041,7 +7041,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="197" spans="1:8">
+    <row r="197" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A197">
         <v>40488444</v>
       </c>
@@ -7067,7 +7067,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="198" spans="1:8">
+    <row r="198" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A198">
         <v>40488841</v>
       </c>
@@ -7093,7 +7093,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="199" spans="1:8">
+    <row r="199" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A199">
         <v>40489905</v>
       </c>
@@ -7119,7 +7119,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="200" spans="1:8">
+    <row r="200" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A200">
         <v>40490483</v>
       </c>
@@ -7145,7 +7145,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="201" spans="1:8">
+    <row r="201" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A201">
         <v>40490956</v>
       </c>
@@ -7171,7 +7171,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="202" spans="1:8">
+    <row r="202" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A202">
         <v>40491011</v>
       </c>
@@ -7197,7 +7197,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="203" spans="1:8">
+    <row r="203" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A203">
         <v>40491478</v>
       </c>
@@ -7223,7 +7223,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="204" spans="1:8">
+    <row r="204" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A204">
         <v>40491529</v>
       </c>
@@ -7249,7 +7249,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="205" spans="1:8">
+    <row r="205" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A205">
         <v>40491967</v>
       </c>
@@ -7275,7 +7275,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="206" spans="1:8">
+    <row r="206" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A206">
         <v>40492025</v>
       </c>
@@ -7301,7 +7301,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="207" spans="1:8">
+    <row r="207" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A207">
         <v>40492189</v>
       </c>
@@ -7327,7 +7327,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="208" spans="1:8">
+    <row r="208" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A208">
         <v>40492453</v>
       </c>
@@ -7353,7 +7353,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="209" spans="1:8">
+    <row r="209" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A209">
         <v>40493447</v>
       </c>
@@ -7379,7 +7379,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="210" spans="1:8">
+    <row r="210" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A210">
         <v>40493451</v>
       </c>
@@ -7405,7 +7405,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="211" spans="1:8">
+    <row r="211" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A211">
         <v>40493459</v>
       </c>
@@ -7431,7 +7431,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="212" spans="1:8">
+    <row r="212" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A212">
         <v>40493487</v>
       </c>
@@ -7457,7 +7457,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="213" spans="1:8">
+    <row r="213" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A213">
         <v>42538529</v>
       </c>
@@ -7483,7 +7483,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="214" spans="1:8">
+    <row r="214" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A214">
         <v>42539157</v>
       </c>
@@ -7509,7 +7509,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="215" spans="1:8">
+    <row r="215" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A215">
         <v>42595751</v>
       </c>
@@ -7535,7 +7535,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="216" spans="1:8">
+    <row r="216" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A216">
         <v>42597024</v>
       </c>
@@ -7561,7 +7561,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="217" spans="1:8">
+    <row r="217" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A217">
         <v>42597038</v>
       </c>
@@ -7587,7 +7587,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="218" spans="1:8">
+    <row r="218" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A218">
         <v>42599737</v>
       </c>
@@ -7613,7 +7613,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="219" spans="1:8">
+    <row r="219" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A219">
         <v>42599746</v>
       </c>
@@ -7639,7 +7639,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="220" spans="1:8">
+    <row r="220" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A220">
         <v>42599749</v>
       </c>
@@ -7665,7 +7665,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="221" spans="1:8">
+    <row r="221" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A221">
         <v>42599750</v>
       </c>
@@ -7691,7 +7691,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="222" spans="1:8">
+    <row r="222" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A222">
         <v>42599795</v>
       </c>
@@ -7717,7 +7717,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="223" spans="1:8">
+    <row r="223" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A223">
         <v>43020504</v>
       </c>
@@ -7743,7 +7743,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="224" spans="1:8">
+    <row r="224" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A224">
         <v>43020626</v>
       </c>
@@ -7769,7 +7769,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="225" spans="1:8">
+    <row r="225" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A225">
         <v>43020627</v>
       </c>
@@ -7795,7 +7795,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="226" spans="1:8">
+    <row r="226" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A226">
         <v>43020628</v>
       </c>
@@ -7821,7 +7821,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="227" spans="1:8">
+    <row r="227" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A227">
         <v>43020629</v>
       </c>
@@ -7847,7 +7847,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="228" spans="1:8">
+    <row r="228" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A228">
         <v>43020630</v>
       </c>
@@ -7873,7 +7873,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="229" spans="1:8">
+    <row r="229" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A229">
         <v>43020882</v>
       </c>
@@ -7899,7 +7899,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="230" spans="1:8">
+    <row r="230" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A230">
         <v>43020903</v>
       </c>
@@ -7925,7 +7925,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="231" spans="1:8">
+    <row r="231" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A231">
         <v>43020913</v>
       </c>
@@ -7951,7 +7951,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="232" spans="1:8">
+    <row r="232" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A232">
         <v>43020914</v>
       </c>
@@ -7977,7 +7977,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="233" spans="1:8">
+    <row r="233" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A233">
         <v>43020915</v>
       </c>
@@ -8003,7 +8003,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="234" spans="1:8">
+    <row r="234" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A234">
         <v>43020916</v>
       </c>
@@ -8029,7 +8029,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="235" spans="1:8">
+    <row r="235" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A235">
         <v>43020917</v>
       </c>
@@ -8055,7 +8055,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="236" spans="1:8">
+    <row r="236" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A236">
         <v>43020957</v>
       </c>
@@ -8081,7 +8081,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="237" spans="1:8">
+    <row r="237" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A237">
         <v>43020959</v>
       </c>
@@ -8107,7 +8107,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="238" spans="1:8">
+    <row r="238" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A238">
         <v>43020960</v>
       </c>
@@ -8133,7 +8133,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="239" spans="1:8">
+    <row r="239" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A239">
         <v>43020962</v>
       </c>
@@ -8159,7 +8159,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="240" spans="1:8">
+    <row r="240" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A240">
         <v>43020964</v>
       </c>
@@ -8185,7 +8185,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="241" spans="1:8">
+    <row r="241" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A241">
         <v>43021070</v>
       </c>
@@ -8211,7 +8211,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="242" spans="1:8">
+    <row r="242" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A242">
         <v>43021708</v>
       </c>
@@ -8237,7 +8237,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="243" spans="1:8">
+    <row r="243" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A243">
         <v>43021806</v>
       </c>
@@ -8263,7 +8263,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="244" spans="1:8">
+    <row r="244" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A244">
         <v>43021943</v>
       </c>
@@ -8289,7 +8289,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="245" spans="1:8">
+    <row r="245" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A245">
         <v>43021944</v>
       </c>
@@ -8315,7 +8315,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="246" spans="1:8">
+    <row r="246" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A246">
         <v>43021945</v>
       </c>
@@ -8341,7 +8341,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="247" spans="1:8">
+    <row r="247" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A247">
         <v>45757096</v>
       </c>
@@ -8367,7 +8367,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="248" spans="1:8">
+    <row r="248" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A248">
         <v>45766079</v>
       </c>
@@ -8393,7 +8393,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="249" spans="1:8">
+    <row r="249" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A249">
         <v>45766080</v>
       </c>
@@ -8419,7 +8419,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="250" spans="1:8">
+    <row r="250" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A250">
         <v>45766081</v>
       </c>
@@ -8445,7 +8445,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="251" spans="1:8">
+    <row r="251" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A251">
         <v>45766082</v>
       </c>
@@ -8471,7 +8471,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="252" spans="1:8">
+    <row r="252" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A252">
         <v>45766083</v>
       </c>
@@ -8497,7 +8497,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="253" spans="1:8">
+    <row r="253" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A253">
         <v>45766084</v>
       </c>
@@ -8523,7 +8523,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="254" spans="1:8">
+    <row r="254" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A254">
         <v>45766087</v>
       </c>
@@ -8549,7 +8549,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="255" spans="1:8">
+    <row r="255" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A255">
         <v>45766089</v>
       </c>
@@ -8575,7 +8575,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="256" spans="1:8">
+    <row r="256" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A256">
         <v>45766092</v>
       </c>
@@ -8601,7 +8601,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="257" spans="1:8">
+    <row r="257" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A257">
         <v>45766095</v>
       </c>
@@ -8627,7 +8627,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="258" spans="1:8">
+    <row r="258" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A258">
         <v>45766099</v>
       </c>
@@ -8653,7 +8653,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="259" spans="1:8">
+    <row r="259" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A259">
         <v>45766124</v>
       </c>
@@ -8679,7 +8679,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="260" spans="1:8">
+    <row r="260" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A260">
         <v>45766125</v>
       </c>
@@ -8705,7 +8705,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="261" spans="1:8">
+    <row r="261" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A261">
         <v>45766126</v>
       </c>
@@ -8731,7 +8731,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="262" spans="1:8">
+    <row r="262" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A262">
         <v>45766136</v>
       </c>
@@ -8757,7 +8757,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="263" spans="1:8">
+    <row r="263" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A263">
         <v>45766181</v>
       </c>
@@ -8783,7 +8783,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="264" spans="1:8">
+    <row r="264" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A264">
         <v>45766182</v>
       </c>
@@ -8809,7 +8809,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="265" spans="1:8">
+    <row r="265" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A265">
         <v>45766185</v>
       </c>
@@ -8835,7 +8835,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="266" spans="1:8">
+    <row r="266" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A266">
         <v>45766186</v>
       </c>
@@ -8861,7 +8861,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="267" spans="1:8">
+    <row r="267" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A267">
         <v>45766205</v>
       </c>
@@ -8887,7 +8887,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="268" spans="1:8">
+    <row r="268" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A268">
         <v>45766206</v>
       </c>
@@ -8913,7 +8913,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="269" spans="1:8">
+    <row r="269" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A269">
         <v>45766207</v>
       </c>
@@ -8939,7 +8939,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="270" spans="1:8">
+    <row r="270" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A270">
         <v>45766210</v>
       </c>
@@ -8965,7 +8965,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="271" spans="1:8">
+    <row r="271" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A271">
         <v>45766211</v>
       </c>
@@ -8991,7 +8991,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="272" spans="1:8">
+    <row r="272" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A272">
         <v>45766213</v>
       </c>
@@ -9017,7 +9017,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="273" spans="1:8">
+    <row r="273" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A273">
         <v>45766214</v>
       </c>
@@ -9043,7 +9043,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="274" spans="1:8">
+    <row r="274" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A274">
         <v>45771317</v>
       </c>
@@ -9069,7 +9069,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="275" spans="1:8">
+    <row r="275" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A275">
         <v>45771321</v>
       </c>
@@ -9095,7 +9095,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="276" spans="1:8">
+    <row r="276" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A276">
         <v>45771323</v>
       </c>
@@ -9121,7 +9121,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="277" spans="1:8">
+    <row r="277" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A277">
         <v>45771326</v>
       </c>
@@ -9147,7 +9147,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="278" spans="1:8">
+    <row r="278" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A278">
         <v>45771327</v>
       </c>
@@ -9173,7 +9173,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="279" spans="1:8">
+    <row r="279" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A279">
         <v>45773080</v>
       </c>
@@ -9207,18 +9207,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G94"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="45" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="44.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="23.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="44.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23.83203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="1" customFormat="1">
+    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>295</v>
       </c>
@@ -9241,7 +9241,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>313007</v>
       </c>
@@ -9264,7 +9264,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>313221</v>
       </c>
@@ -9287,7 +9287,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>314054</v>
       </c>
@@ -9310,7 +9310,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>314054</v>
       </c>
@@ -9333,7 +9333,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>314054</v>
       </c>
@@ -9356,7 +9356,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>314054</v>
       </c>
@@ -9379,7 +9379,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>314368</v>
       </c>
@@ -9402,7 +9402,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>314368</v>
       </c>
@@ -9425,7 +9425,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>314368</v>
       </c>
@@ -9448,7 +9448,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>314457</v>
       </c>
@@ -9471,7 +9471,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>315282</v>
       </c>
@@ -9494,7 +9494,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>315282</v>
       </c>
@@ -9517,7 +9517,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>315282</v>
       </c>
@@ -9540,7 +9540,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>315564</v>
       </c>
@@ -9563,7 +9563,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>315564</v>
       </c>
@@ -9586,7 +9586,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>315564</v>
       </c>
@@ -9609,7 +9609,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>317890</v>
       </c>
@@ -9632,7 +9632,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>318689</v>
       </c>
@@ -9655,7 +9655,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>318776</v>
       </c>
@@ -9678,7 +9678,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>318776</v>
       </c>
@@ -9701,7 +9701,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>318776</v>
       </c>
@@ -9724,7 +9724,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>320115</v>
       </c>
@@ -9747,7 +9747,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>320115</v>
       </c>
@@ -9770,7 +9770,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>320115</v>
       </c>
@@ -9793,7 +9793,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>320416</v>
       </c>
@@ -9816,7 +9816,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>320416</v>
       </c>
@@ -9839,7 +9839,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>320416</v>
       </c>
@@ -9862,7 +9862,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>320429</v>
       </c>
@@ -9885,7 +9885,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>321041</v>
       </c>
@@ -9908,7 +9908,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>321041</v>
       </c>
@@ -9931,7 +9931,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>321041</v>
       </c>
@@ -9954,7 +9954,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>321107</v>
       </c>
@@ -9977,7 +9977,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>321107</v>
       </c>
@@ -10000,7 +10000,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>321107</v>
       </c>
@@ -10023,7 +10023,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>439834</v>
       </c>
@@ -10046,7 +10046,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>439834</v>
       </c>
@@ -10069,7 +10069,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>439834</v>
       </c>
@@ -10092,7 +10092,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>443962</v>
       </c>
@@ -10115,7 +10115,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>443962</v>
       </c>
@@ -10138,7 +10138,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>443962</v>
       </c>
@@ -10161,7 +10161,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>443962</v>
       </c>
@@ -10184,7 +10184,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>443962</v>
       </c>
@@ -10207,7 +10207,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>4006971</v>
       </c>
@@ -10230,7 +10230,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>4006971</v>
       </c>
@@ -10253,7 +10253,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>4006971</v>
       </c>
@@ -10276,7 +10276,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>4012483</v>
       </c>
@@ -10299,7 +10299,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>4035467</v>
       </c>
@@ -10322,7 +10322,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="49" spans="1:7">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>4069183</v>
       </c>
@@ -10345,7 +10345,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="50" spans="1:7">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>4108085</v>
       </c>
@@ -10368,7 +10368,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="51" spans="1:7">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>4108085</v>
       </c>
@@ -10391,7 +10391,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="52" spans="1:7">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>4108085</v>
       </c>
@@ -10414,7 +10414,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="53" spans="1:7">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>4108164</v>
       </c>
@@ -10437,7 +10437,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="54" spans="1:7">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>4108235</v>
       </c>
@@ -10460,7 +10460,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="55" spans="1:7">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>4108659</v>
       </c>
@@ -10483,7 +10483,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="56" spans="1:7">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>4108659</v>
       </c>
@@ -10506,7 +10506,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="57" spans="1:7">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>4108659</v>
       </c>
@@ -10529,7 +10529,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="58" spans="1:7">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>4108815</v>
       </c>
@@ -10552,7 +10552,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="59" spans="1:7">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>4108819</v>
       </c>
@@ -10575,7 +10575,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="60" spans="1:7">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>4109324</v>
       </c>
@@ -10598,7 +10598,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="61" spans="1:7">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>4111098</v>
       </c>
@@ -10621,7 +10621,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="62" spans="1:7">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>4111099</v>
       </c>
@@ -10644,7 +10644,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="63" spans="1:7">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>4111409</v>
       </c>
@@ -10667,7 +10667,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="64" spans="1:7">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>4111409</v>
       </c>
@@ -10690,7 +10690,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="65" spans="1:7">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A65">
         <v>4111409</v>
       </c>
@@ -10713,7 +10713,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="66" spans="1:7">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>4111412</v>
       </c>
@@ -10736,7 +10736,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="67" spans="1:7">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>4111412</v>
       </c>
@@ -10759,7 +10759,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="68" spans="1:7">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>4111412</v>
       </c>
@@ -10782,7 +10782,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="69" spans="1:7">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>4111414</v>
       </c>
@@ -10805,7 +10805,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="70" spans="1:7">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>4111416</v>
       </c>
@@ -10828,7 +10828,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="71" spans="1:7">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A71">
         <v>4111416</v>
       </c>
@@ -10851,7 +10851,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="72" spans="1:7">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A72">
         <v>4111416</v>
       </c>
@@ -10874,7 +10874,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="73" spans="1:7">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A73">
         <v>4111565</v>
       </c>
@@ -10897,7 +10897,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="74" spans="1:7">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A74">
         <v>4112093</v>
       </c>
@@ -10920,7 +10920,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="75" spans="1:7">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A75">
         <v>4113295</v>
       </c>
@@ -10943,7 +10943,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="76" spans="1:7">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A76">
         <v>4143607</v>
       </c>
@@ -10966,7 +10966,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="77" spans="1:7">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A77">
         <v>4147787</v>
       </c>
@@ -10989,7 +10989,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="78" spans="1:7">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A78">
         <v>4147787</v>
       </c>
@@ -11012,7 +11012,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="79" spans="1:7">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A79">
         <v>4189343</v>
       </c>
@@ -11035,7 +11035,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="80" spans="1:7">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A80">
         <v>4189343</v>
       </c>
@@ -11058,7 +11058,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="81" spans="1:7">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A81">
         <v>4195677</v>
       </c>
@@ -11081,7 +11081,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="82" spans="1:7">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A82">
         <v>4195677</v>
       </c>
@@ -11104,7 +11104,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="83" spans="1:7">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A83">
         <v>4195677</v>
       </c>
@@ -11127,7 +11127,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="84" spans="1:7">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A84">
         <v>4195690</v>
       </c>
@@ -11150,7 +11150,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="85" spans="1:7">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A85">
         <v>4218450</v>
       </c>
@@ -11173,7 +11173,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="86" spans="1:7">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A86">
         <v>4230774</v>
       </c>
@@ -11196,7 +11196,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="87" spans="1:7">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A87">
         <v>4230774</v>
       </c>
@@ -11219,7 +11219,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="88" spans="1:7">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A88">
         <v>4230774</v>
       </c>
@@ -11242,7 +11242,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="89" spans="1:7">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A89">
         <v>4237202</v>
       </c>
@@ -11265,7 +11265,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="90" spans="1:7">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A90">
         <v>4237202</v>
       </c>
@@ -11288,7 +11288,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="91" spans="1:7">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A91">
         <v>4237202</v>
       </c>
@@ -11311,7 +11311,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="92" spans="1:7">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A92">
         <v>4244173</v>
       </c>
@@ -11334,7 +11334,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="93" spans="1:7">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A93">
         <v>4246951</v>
       </c>
@@ -11357,7 +11357,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="94" spans="1:7">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A94">
         <v>4312621</v>
       </c>
@@ -11388,18 +11388,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G31"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="45" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="45.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="23.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="45.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23.83203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="1" customFormat="1">
+    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>295</v>
       </c>
@@ -11422,7 +11422,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>259123</v>
       </c>
@@ -11445,7 +11445,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>313007</v>
       </c>
@@ -11468,7 +11468,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>313221</v>
       </c>
@@ -11491,7 +11491,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>314054</v>
       </c>
@@ -11514,7 +11514,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>314054</v>
       </c>
@@ -11537,7 +11537,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>314054</v>
       </c>
@@ -11560,7 +11560,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>314457</v>
       </c>
@@ -11583,7 +11583,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>315282</v>
       </c>
@@ -11606,7 +11606,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>315282</v>
       </c>
@@ -11629,7 +11629,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>315282</v>
       </c>
@@ -11652,7 +11652,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>315564</v>
       </c>
@@ -11675,7 +11675,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>318776</v>
       </c>
@@ -11698,7 +11698,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>320429</v>
       </c>
@@ -11721,7 +11721,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>321107</v>
       </c>
@@ -11744,7 +11744,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>439834</v>
       </c>
@@ -11767,7 +11767,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>443962</v>
       </c>
@@ -11790,7 +11790,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>4006971</v>
       </c>
@@ -11813,7 +11813,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>4035467</v>
       </c>
@@ -11836,7 +11836,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>4040820</v>
       </c>
@@ -11859,7 +11859,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>4108085</v>
       </c>
@@ -11882,7 +11882,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>4108235</v>
       </c>
@@ -11905,7 +11905,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>4108819</v>
       </c>
@@ -11928,7 +11928,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>4111099</v>
       </c>
@@ -11951,7 +11951,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>4111412</v>
       </c>
@@ -11974,7 +11974,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>4111414</v>
       </c>
@@ -11997,7 +11997,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>4111565</v>
       </c>
@@ -12020,7 +12020,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>4147787</v>
       </c>
@@ -12043,7 +12043,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>4189343</v>
       </c>
@@ -12066,7 +12066,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>4237202</v>
       </c>
@@ -12089,7 +12089,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>4301373</v>
       </c>
@@ -12587,6 +12587,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <Math_Settings xmlns="3aedf1c0-925e-4524-a733-b26409c497aa" xsi:nil="true"/>
@@ -12648,23 +12657,40 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EEC1AC94-7F34-4D7E-970E-DBF576DB354D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EEC1AC94-7F34-4D7E-970E-DBF576DB354D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="3aedf1c0-925e-4524-a733-b26409c497aa"/>
+    <ds:schemaRef ds:uri="b3804bb9-11fa-4e2e-86f5-8d7bf731dfbd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5D696001-9C62-4573-8955-808EF4AF9AEB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{140DA760-0CDF-4C85-B7E0-B3359DD65875}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{140DA760-0CDF-4C85-B7E0-B3359DD65875}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5D696001-9C62-4573-8955-808EF4AF9AEB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3aedf1c0-925e-4524-a733-b26409c497aa"/>
+    <ds:schemaRef ds:uri="b3804bb9-11fa-4e2e-86f5-8d7bf731dfbd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/diagnostics_code/aortic_valve_disease_codes_reviewed.xlsx
+++ b/diagnostics_code/aortic_valve_disease_codes_reviewed.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/orms0426/Documents/GitHub/HERON-UK-02-002-CVDValveReplacement/diagnostics_code/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC1D3C2D-6E06-F647-843D-6F7A3B85DFDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9119930F-6483-BC41-8AA7-E8D667155A41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="680" windowWidth="23040" windowHeight="19080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1339,7 +1339,7 @@
         <v>14</v>
       </c>
       <c r="G3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H3" t="s">
         <v>16</v>

--- a/diagnostics_code/aortic_valve_disease_codes_reviewed.xlsx
+++ b/diagnostics_code/aortic_valve_disease_codes_reviewed.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/orms0426/Documents/GitHub/HERON-UK-02-002-CVDValveReplacement/diagnostics_code/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{539A98EE-02A2-9647-9938-B9ACFAA66911}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C678EB24-EC7E-ED4E-97C5-FB9C4E455FAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="21460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="20360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$A$271</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$L$1:$L$271</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2982" uniqueCount="290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3253" uniqueCount="291">
   <si>
     <t>concept_id</t>
   </si>
@@ -906,6 +906,9 @@
   </si>
   <si>
     <t>aortic_stenosis_congenital</t>
+  </si>
+  <si>
+    <t>aortic_insufficiency_congenital</t>
   </si>
 </sst>
 </file>
@@ -1258,7 +1261,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L271"/>
+  <dimension ref="A1:M271"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="116.83203125" customWidth="1"/>
@@ -1269,10 +1272,10 @@
     <col min="8" max="8" width="15" customWidth="1"/>
     <col min="9" max="9" width="18.1640625" customWidth="1"/>
     <col min="10" max="10" width="24.1640625" customWidth="1"/>
-    <col min="11" max="12" width="18.5" customWidth="1"/>
+    <col min="11" max="13" width="18.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1309,8 +1312,11 @@
       <c r="L1" t="s">
         <v>287</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M1" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>259123</v>
       </c>
@@ -1347,8 +1353,11 @@
       <c r="L2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>313007</v>
       </c>
@@ -1385,8 +1394,11 @@
       <c r="L3" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>313221</v>
       </c>
@@ -1423,8 +1435,11 @@
       <c r="L4" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>314054</v>
       </c>
@@ -1461,8 +1476,11 @@
       <c r="L5" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>314368</v>
       </c>
@@ -1499,8 +1517,11 @@
       <c r="L6" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>314457</v>
       </c>
@@ -1537,8 +1558,11 @@
       <c r="L7" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>315282</v>
       </c>
@@ -1575,8 +1599,11 @@
       <c r="L8" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>315564</v>
       </c>
@@ -1613,8 +1640,11 @@
       <c r="L9" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>317890</v>
       </c>
@@ -1651,8 +1681,11 @@
       <c r="L10" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>318689</v>
       </c>
@@ -1689,8 +1722,11 @@
       <c r="L11" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M11" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>318776</v>
       </c>
@@ -1727,8 +1763,11 @@
       <c r="L12" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>320115</v>
       </c>
@@ -1765,8 +1804,11 @@
       <c r="L13" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>320416</v>
       </c>
@@ -1803,8 +1845,11 @@
       <c r="L14" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M14" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>320429</v>
       </c>
@@ -1841,8 +1886,11 @@
       <c r="L15" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M15" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>321041</v>
       </c>
@@ -1879,8 +1927,11 @@
       <c r="L16" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M16" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>321107</v>
       </c>
@@ -1917,8 +1968,11 @@
       <c r="L17" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M17" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>439834</v>
       </c>
@@ -1955,8 +2009,11 @@
       <c r="L18" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M18" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>443962</v>
       </c>
@@ -1993,8 +2050,11 @@
       <c r="L19" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M19" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>600625</v>
       </c>
@@ -2031,8 +2091,11 @@
       <c r="L20" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M20" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>604345</v>
       </c>
@@ -2069,8 +2132,11 @@
       <c r="L21" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M21" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>605551</v>
       </c>
@@ -2107,8 +2173,11 @@
       <c r="L22" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M22" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>605552</v>
       </c>
@@ -2145,8 +2214,11 @@
       <c r="L23" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M23" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>605778</v>
       </c>
@@ -2183,8 +2255,11 @@
       <c r="L24" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M24" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>605897</v>
       </c>
@@ -2221,8 +2296,11 @@
       <c r="L25" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M25" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>606038</v>
       </c>
@@ -2259,8 +2337,11 @@
       <c r="L26" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M26" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>606159</v>
       </c>
@@ -2297,8 +2378,11 @@
       <c r="L27" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M27" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>607641</v>
       </c>
@@ -2335,8 +2419,11 @@
       <c r="L28" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M28" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>618992</v>
       </c>
@@ -2373,8 +2460,11 @@
       <c r="L29" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M29" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>618994</v>
       </c>
@@ -2411,8 +2501,11 @@
       <c r="L30" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M30" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>619135</v>
       </c>
@@ -2449,8 +2542,11 @@
       <c r="L31" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M31" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>619141</v>
       </c>
@@ -2487,8 +2583,11 @@
       <c r="L32" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M32" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>1244580</v>
       </c>
@@ -2525,8 +2624,11 @@
       <c r="L33" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M33" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>1244581</v>
       </c>
@@ -2563,8 +2665,11 @@
       <c r="L34" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M34" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>3654574</v>
       </c>
@@ -2601,8 +2706,11 @@
       <c r="L35" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M35" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>3654575</v>
       </c>
@@ -2639,8 +2747,11 @@
       <c r="L36" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M36" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>3654576</v>
       </c>
@@ -2677,8 +2788,11 @@
       <c r="L37" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M37" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>3654726</v>
       </c>
@@ -2715,8 +2829,11 @@
       <c r="L38" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M38" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>3654727</v>
       </c>
@@ -2753,8 +2870,11 @@
       <c r="L39" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M39" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>3654728</v>
       </c>
@@ -2791,8 +2911,11 @@
       <c r="L40" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M40" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>3654729</v>
       </c>
@@ -2829,8 +2952,11 @@
       <c r="L41" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M41" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>3654730</v>
       </c>
@@ -2867,8 +2993,11 @@
       <c r="L42" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M42" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>3654731</v>
       </c>
@@ -2905,8 +3034,11 @@
       <c r="L43" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M43" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>3654795</v>
       </c>
@@ -2943,8 +3075,11 @@
       <c r="L44" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M44" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>3654796</v>
       </c>
@@ -2981,8 +3116,11 @@
       <c r="L45" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M45" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>3654797</v>
       </c>
@@ -3019,8 +3157,11 @@
       <c r="L46" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M46" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>3654798</v>
       </c>
@@ -3057,8 +3198,11 @@
       <c r="L47" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M47" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>3654799</v>
       </c>
@@ -3095,8 +3239,11 @@
       <c r="L48" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M48" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>3654800</v>
       </c>
@@ -3133,8 +3280,11 @@
       <c r="L49" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M49" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>3654940</v>
       </c>
@@ -3171,8 +3321,11 @@
       <c r="L50" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M50" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>3654955</v>
       </c>
@@ -3209,8 +3362,11 @@
       <c r="L51" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M51" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>3656075</v>
       </c>
@@ -3247,8 +3403,11 @@
       <c r="L52" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M52" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>3656077</v>
       </c>
@@ -3285,8 +3444,11 @@
       <c r="L53" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M53" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>3656079</v>
       </c>
@@ -3323,8 +3485,11 @@
       <c r="L54" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M54" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>3656100</v>
       </c>
@@ -3361,8 +3526,11 @@
       <c r="L55" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M55" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>3656127</v>
       </c>
@@ -3399,8 +3567,11 @@
       <c r="L56" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M56" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>3656136</v>
       </c>
@@ -3437,8 +3608,11 @@
       <c r="L57" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M57" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>3656142</v>
       </c>
@@ -3475,8 +3649,11 @@
       <c r="L58" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M58" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>4006971</v>
       </c>
@@ -3513,8 +3690,11 @@
       <c r="L59" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M59" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>4012483</v>
       </c>
@@ -3551,8 +3731,11 @@
       <c r="L60" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M60" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>4030224</v>
       </c>
@@ -3589,8 +3772,11 @@
       <c r="L61" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M61" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>4035467</v>
       </c>
@@ -3627,8 +3813,11 @@
       <c r="L62" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M62" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>4040820</v>
       </c>
@@ -3665,8 +3854,11 @@
       <c r="L63" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M63" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>4048213</v>
       </c>
@@ -3703,8 +3895,11 @@
       <c r="L64" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M64" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A65">
         <v>4058384</v>
       </c>
@@ -3741,8 +3936,11 @@
       <c r="L65" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M65" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>4069183</v>
       </c>
@@ -3779,8 +3977,11 @@
       <c r="L66" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M66" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>4081037</v>
       </c>
@@ -3817,8 +4018,11 @@
       <c r="L67" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M67" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>4102992</v>
       </c>
@@ -3855,8 +4059,11 @@
       <c r="L68" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M68" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>4103319</v>
       </c>
@@ -3893,8 +4100,11 @@
       <c r="L69" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M69" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>4108085</v>
       </c>
@@ -3931,8 +4141,11 @@
       <c r="L70" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M70" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A71">
         <v>4108164</v>
       </c>
@@ -3969,8 +4182,11 @@
       <c r="L71" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M71" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A72">
         <v>4108165</v>
       </c>
@@ -4007,8 +4223,11 @@
       <c r="L72" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M72" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A73">
         <v>4108235</v>
       </c>
@@ -4045,8 +4264,11 @@
       <c r="L73" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M73" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A74">
         <v>4108595</v>
       </c>
@@ -4083,8 +4305,11 @@
       <c r="L74" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M74" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A75">
         <v>4108596</v>
       </c>
@@ -4121,8 +4346,11 @@
       <c r="L75" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M75" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A76">
         <v>4108659</v>
       </c>
@@ -4159,8 +4387,11 @@
       <c r="L76" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M76" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A77">
         <v>4108723</v>
       </c>
@@ -4197,8 +4428,11 @@
       <c r="L77" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M77" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="78" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A78">
         <v>4108729</v>
       </c>
@@ -4235,8 +4469,11 @@
       <c r="L78" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M78" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A79">
         <v>4108730</v>
       </c>
@@ -4273,8 +4510,11 @@
       <c r="L79" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M79" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="80" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A80">
         <v>4108731</v>
       </c>
@@ -4311,8 +4551,11 @@
       <c r="L80" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M80" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="81" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A81">
         <v>4108732</v>
       </c>
@@ -4349,8 +4592,11 @@
       <c r="L81" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M81" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="82" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A82">
         <v>4108815</v>
       </c>
@@ -4387,8 +4633,11 @@
       <c r="L82" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M82" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="83" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A83">
         <v>4108819</v>
       </c>
@@ -4425,8 +4674,11 @@
       <c r="L83" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M83" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="84" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A84">
         <v>4109202</v>
       </c>
@@ -4463,8 +4715,11 @@
       <c r="L84" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M84" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="85" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A85">
         <v>4109324</v>
       </c>
@@ -4501,8 +4756,11 @@
       <c r="L85" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M85" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="86" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A86">
         <v>4109338</v>
       </c>
@@ -4539,8 +4797,11 @@
       <c r="L86" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M86" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="87" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A87">
         <v>4109340</v>
       </c>
@@ -4577,8 +4838,11 @@
       <c r="L87" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M87" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="88" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A88">
         <v>4109341</v>
       </c>
@@ -4615,8 +4879,11 @@
       <c r="L88" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M88" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="89" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A89">
         <v>4109347</v>
       </c>
@@ -4653,8 +4920,11 @@
       <c r="L89" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M89" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="90" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A90">
         <v>4109463</v>
       </c>
@@ -4691,8 +4961,11 @@
       <c r="L90" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M90" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="91" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A91">
         <v>4111098</v>
       </c>
@@ -4729,8 +5002,11 @@
       <c r="L91" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M91" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="92" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A92">
         <v>4111099</v>
       </c>
@@ -4767,8 +5043,11 @@
       <c r="L92" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M92" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="93" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A93">
         <v>4111409</v>
       </c>
@@ -4805,8 +5084,11 @@
       <c r="L93" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M93" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="94" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A94">
         <v>4111412</v>
       </c>
@@ -4843,8 +5125,11 @@
       <c r="L94" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M94" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="95" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A95">
         <v>4111414</v>
       </c>
@@ -4881,8 +5166,11 @@
       <c r="L95" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M95" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="96" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A96">
         <v>4111416</v>
       </c>
@@ -4919,8 +5207,11 @@
       <c r="L96" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M96" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="97" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A97">
         <v>4111565</v>
       </c>
@@ -4957,8 +5248,11 @@
       <c r="L97" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M97" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="98" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A98">
         <v>4112083</v>
       </c>
@@ -4995,8 +5289,11 @@
       <c r="L98" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M98" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="99" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A99">
         <v>4112091</v>
       </c>
@@ -5033,8 +5330,11 @@
       <c r="L99" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M99" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="100" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A100">
         <v>4112092</v>
       </c>
@@ -5071,8 +5371,11 @@
       <c r="L100" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M100" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="101" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A101">
         <v>4112093</v>
       </c>
@@ -5109,8 +5412,11 @@
       <c r="L101" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="102" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M101" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="102" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A102">
         <v>4113295</v>
       </c>
@@ -5147,8 +5453,11 @@
       <c r="L102" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="103" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M102" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="103" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A103">
         <v>4119463</v>
       </c>
@@ -5185,8 +5494,11 @@
       <c r="L103" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="104" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M103" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="104" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A104">
         <v>4119589</v>
       </c>
@@ -5223,8 +5535,11 @@
       <c r="L104" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="105" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M104" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="105" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A105">
         <v>4119956</v>
       </c>
@@ -5261,8 +5576,11 @@
       <c r="L105" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="106" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M105" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="106" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A106">
         <v>4119957</v>
       </c>
@@ -5299,8 +5617,11 @@
       <c r="L106" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="107" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M106" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="107" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A107">
         <v>4121472</v>
       </c>
@@ -5337,8 +5658,11 @@
       <c r="L107" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="108" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M107" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="108" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A108">
         <v>4124690</v>
       </c>
@@ -5375,8 +5699,11 @@
       <c r="L108" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="109" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M108" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="109" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A109">
         <v>4125004</v>
       </c>
@@ -5413,8 +5740,11 @@
       <c r="L109" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M109" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="110" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A110">
         <v>4133509</v>
       </c>
@@ -5451,8 +5781,11 @@
       <c r="L110" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="111" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M110" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="111" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A111">
         <v>4143607</v>
       </c>
@@ -5489,8 +5822,11 @@
       <c r="L111" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="112" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M111" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="112" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A112">
         <v>4144901</v>
       </c>
@@ -5527,8 +5863,11 @@
       <c r="L112" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="113" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M112" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="113" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A113">
         <v>4147787</v>
       </c>
@@ -5565,8 +5904,11 @@
       <c r="L113" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="114" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M113" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="114" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A114">
         <v>4152384</v>
       </c>
@@ -5603,8 +5945,11 @@
       <c r="L114" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="115" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M114" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="115" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A115">
         <v>4154293</v>
       </c>
@@ -5641,8 +5986,11 @@
       <c r="L115" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="116" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M115" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="116" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A116">
         <v>4155964</v>
       </c>
@@ -5679,8 +6027,11 @@
       <c r="L116" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="117" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M116" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="117" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A117">
         <v>4156119</v>
       </c>
@@ -5717,8 +6068,11 @@
       <c r="L117" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="118" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M117" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="118" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A118">
         <v>4161245</v>
       </c>
@@ -5755,8 +6109,11 @@
       <c r="L118" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="119" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M118" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="119" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A119">
         <v>4161458</v>
       </c>
@@ -5793,8 +6150,11 @@
       <c r="L119" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="120" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M119" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="120" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A120">
         <v>4161459</v>
       </c>
@@ -5831,8 +6191,11 @@
       <c r="L120" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="121" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M120" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="121" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A121">
         <v>4161975</v>
       </c>
@@ -5869,8 +6232,11 @@
       <c r="L121" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="122" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M121" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="122" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A122">
         <v>4172866</v>
       </c>
@@ -5907,8 +6273,11 @@
       <c r="L122" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="123" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M122" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="123" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A123">
         <v>4181949</v>
       </c>
@@ -5945,8 +6314,11 @@
       <c r="L123" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="124" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M123" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="124" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A124">
         <v>4182110</v>
       </c>
@@ -5983,8 +6355,11 @@
       <c r="L124" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="125" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M124" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="125" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A125">
         <v>4188554</v>
       </c>
@@ -6021,8 +6396,11 @@
       <c r="L125" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="126" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M125" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="126" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A126">
         <v>4189343</v>
       </c>
@@ -6059,8 +6437,11 @@
       <c r="L126" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="127" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M126" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="127" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A127">
         <v>4189522</v>
       </c>
@@ -6097,8 +6478,11 @@
       <c r="L127" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="128" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M127" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="128" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A128">
         <v>4195677</v>
       </c>
@@ -6135,8 +6519,11 @@
       <c r="L128" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="129" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M128" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="129" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A129">
         <v>4195690</v>
       </c>
@@ -6173,8 +6560,11 @@
       <c r="L129" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="130" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M129" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="130" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A130">
         <v>4197259</v>
       </c>
@@ -6211,8 +6601,11 @@
       <c r="L130" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="131" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M130" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="131" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A131">
         <v>4207052</v>
       </c>
@@ -6249,8 +6642,11 @@
       <c r="L131" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="132" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M131" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="132" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A132">
         <v>4215619</v>
       </c>
@@ -6287,8 +6683,11 @@
       <c r="L132" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="133" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M132" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="133" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A133">
         <v>4218450</v>
       </c>
@@ -6325,8 +6724,11 @@
       <c r="L133" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="134" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M133" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="134" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A134">
         <v>4219047</v>
       </c>
@@ -6363,8 +6765,11 @@
       <c r="L134" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="135" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M134" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="135" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A135">
         <v>4230774</v>
       </c>
@@ -6401,8 +6806,11 @@
       <c r="L135" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="136" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M135" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="136" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A136">
         <v>4231324</v>
       </c>
@@ -6439,8 +6847,11 @@
       <c r="L136" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="137" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M136" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="137" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A137">
         <v>4231818</v>
       </c>
@@ -6477,8 +6888,11 @@
       <c r="L137" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="138" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M137" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="138" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A138">
         <v>4237202</v>
       </c>
@@ -6515,8 +6929,11 @@
       <c r="L138" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="139" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M138" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="139" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A139">
         <v>4242036</v>
       </c>
@@ -6553,8 +6970,11 @@
       <c r="L139" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="140" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M139" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="140" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A140">
         <v>4244173</v>
       </c>
@@ -6591,8 +7011,11 @@
       <c r="L140" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="141" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M140" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="141" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A141">
         <v>4244437</v>
       </c>
@@ -6629,8 +7052,11 @@
       <c r="L141" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="142" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M141" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="142" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A142">
         <v>4244935</v>
       </c>
@@ -6667,8 +7093,11 @@
       <c r="L142" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="143" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M142" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="143" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A143">
         <v>4244966</v>
       </c>
@@ -6705,8 +7134,11 @@
       <c r="L143" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="144" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M143" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="144" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A144">
         <v>4245692</v>
       </c>
@@ -6743,8 +7175,11 @@
       <c r="L144" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="145" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M144" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="145" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A145">
         <v>4246657</v>
       </c>
@@ -6781,8 +7216,11 @@
       <c r="L145" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="146" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M145" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="146" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A146">
         <v>4246951</v>
       </c>
@@ -6819,8 +7257,11 @@
       <c r="L146" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="147" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M146" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="147" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A147">
         <v>4259295</v>
       </c>
@@ -6857,8 +7298,11 @@
       <c r="L147" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="148" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M147" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="148" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A148">
         <v>4298429</v>
       </c>
@@ -6895,8 +7339,11 @@
       <c r="L148" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="149" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M148" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="149" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A149">
         <v>4301373</v>
       </c>
@@ -6933,8 +7380,11 @@
       <c r="L149" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="150" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M149" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="150" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A150">
         <v>4304541</v>
       </c>
@@ -6971,8 +7421,11 @@
       <c r="L150" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="151" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M150" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="151" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A151">
         <v>4305961</v>
       </c>
@@ -7009,8 +7462,11 @@
       <c r="L151" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="152" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M151" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="152" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A152">
         <v>4312621</v>
       </c>
@@ -7047,8 +7503,11 @@
       <c r="L152" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="153" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M152" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="153" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A153">
         <v>4324608</v>
       </c>
@@ -7085,8 +7544,11 @@
       <c r="L153" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="154" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M153" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="154" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A154">
         <v>4324704</v>
       </c>
@@ -7123,8 +7585,11 @@
       <c r="L154" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="155" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M154" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="155" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A155">
         <v>4337282</v>
       </c>
@@ -7161,8 +7626,11 @@
       <c r="L155" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="156" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M155" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="156" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A156">
         <v>4353740</v>
       </c>
@@ -7199,8 +7667,11 @@
       <c r="L156" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="157" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M156" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="157" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A157">
         <v>4353743</v>
       </c>
@@ -7237,8 +7708,11 @@
       <c r="L157" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="158" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M157" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="158" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A158">
         <v>4353822</v>
       </c>
@@ -7275,8 +7749,11 @@
       <c r="L158" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="159" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M158" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="159" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A159">
         <v>4354063</v>
       </c>
@@ -7313,8 +7790,11 @@
       <c r="L159" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="160" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M159" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="160" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A160">
         <v>4354064</v>
       </c>
@@ -7351,8 +7831,11 @@
       <c r="L160" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="161" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M160" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="161" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A161">
         <v>4354065</v>
       </c>
@@ -7389,8 +7872,11 @@
       <c r="L161" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="162" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M161" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="162" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A162">
         <v>4354066</v>
       </c>
@@ -7427,8 +7913,11 @@
       <c r="L162" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="163" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M162" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="163" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A163">
         <v>35622773</v>
       </c>
@@ -7465,8 +7954,11 @@
       <c r="L163" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="164" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M163" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="164" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A164">
         <v>36674716</v>
       </c>
@@ -7503,8 +7995,11 @@
       <c r="L164" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="165" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M164" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="165" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A165">
         <v>36674972</v>
       </c>
@@ -7541,8 +8036,11 @@
       <c r="L165" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="166" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M165" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="166" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A166">
         <v>36684984</v>
       </c>
@@ -7579,8 +8077,11 @@
       <c r="L166" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="167" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M166" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="167" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A167">
         <v>36715123</v>
       </c>
@@ -7617,8 +8118,11 @@
       <c r="L167" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="168" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M167" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="168" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A168">
         <v>37163073</v>
       </c>
@@ -7655,8 +8159,11 @@
       <c r="L168" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="169" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M168" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="169" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A169">
         <v>37163275</v>
       </c>
@@ -7693,8 +8200,11 @@
       <c r="L169" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="170" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M169" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="170" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A170">
         <v>37165735</v>
       </c>
@@ -7731,8 +8241,11 @@
       <c r="L170" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="171" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M170" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="171" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A171">
         <v>37204437</v>
       </c>
@@ -7769,8 +8282,11 @@
       <c r="L171" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="172" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M171" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="172" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A172">
         <v>40482894</v>
       </c>
@@ -7807,8 +8323,11 @@
       <c r="L172" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="173" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M172" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="173" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A173">
         <v>40482925</v>
       </c>
@@ -7845,8 +8364,11 @@
       <c r="L173" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="174" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M173" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="174" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A174">
         <v>40483337</v>
       </c>
@@ -7883,8 +8405,11 @@
       <c r="L174" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="175" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M174" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="175" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A175">
         <v>40484273</v>
       </c>
@@ -7921,8 +8446,11 @@
       <c r="L175" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="176" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M175" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="176" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A176">
         <v>40484305</v>
       </c>
@@ -7959,8 +8487,11 @@
       <c r="L176" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="177" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M176" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="177" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A177">
         <v>40486044</v>
       </c>
@@ -7997,8 +8528,11 @@
       <c r="L177" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="178" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M177" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="178" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A178">
         <v>40486056</v>
       </c>
@@ -8035,8 +8569,11 @@
       <c r="L178" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="179" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M178" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="179" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A179">
         <v>40486057</v>
       </c>
@@ -8073,8 +8610,11 @@
       <c r="L179" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="180" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M179" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="180" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A180">
         <v>40486071</v>
       </c>
@@ -8111,8 +8651,11 @@
       <c r="L180" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="181" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M180" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="181" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A181">
         <v>40486073</v>
       </c>
@@ -8149,8 +8692,11 @@
       <c r="L181" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="182" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M181" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="182" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A182">
         <v>40486608</v>
       </c>
@@ -8187,8 +8733,11 @@
       <c r="L182" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="183" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M182" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="183" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A183">
         <v>40486635</v>
       </c>
@@ -8225,8 +8774,11 @@
       <c r="L183" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="184" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M183" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="184" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A184">
         <v>40487107</v>
       </c>
@@ -8263,8 +8815,11 @@
       <c r="L184" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="185" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M184" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="185" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A185">
         <v>40487183</v>
       </c>
@@ -8301,8 +8856,11 @@
       <c r="L185" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="186" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M185" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="186" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A186">
         <v>40487184</v>
       </c>
@@ -8339,8 +8897,11 @@
       <c r="L186" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="187" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M186" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="187" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A187">
         <v>40487186</v>
       </c>
@@ -8377,8 +8938,11 @@
       <c r="L187" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="188" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M187" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="188" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A188">
         <v>40487600</v>
       </c>
@@ -8415,8 +8979,11 @@
       <c r="L188" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="189" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M188" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="189" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A189">
         <v>40487652</v>
       </c>
@@ -8453,8 +9020,11 @@
       <c r="L189" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="190" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M189" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="190" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A190">
         <v>40487653</v>
       </c>
@@ -8491,8 +9061,11 @@
       <c r="L190" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="191" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M190" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="191" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A191">
         <v>40487654</v>
       </c>
@@ -8529,8 +9102,11 @@
       <c r="L191" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="192" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M191" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="192" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A192">
         <v>40487672</v>
       </c>
@@ -8567,8 +9143,11 @@
       <c r="L192" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="193" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M192" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="193" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A193">
         <v>40487966</v>
       </c>
@@ -8605,8 +9184,11 @@
       <c r="L193" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="194" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M193" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="194" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A194">
         <v>40487992</v>
       </c>
@@ -8643,8 +9225,11 @@
       <c r="L194" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="195" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M194" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="195" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A195">
         <v>40488014</v>
       </c>
@@ -8681,8 +9266,11 @@
       <c r="L195" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="196" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M195" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="196" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A196">
         <v>40488397</v>
       </c>
@@ -8719,8 +9307,11 @@
       <c r="L196" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="197" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M196" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="197" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A197">
         <v>40488444</v>
       </c>
@@ -8757,8 +9348,11 @@
       <c r="L197" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="198" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M197" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="198" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A198">
         <v>40488841</v>
       </c>
@@ -8795,8 +9389,11 @@
       <c r="L198" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="199" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M198" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="199" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A199">
         <v>40489905</v>
       </c>
@@ -8833,8 +9430,11 @@
       <c r="L199" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="200" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M199" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="200" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A200">
         <v>40490483</v>
       </c>
@@ -8871,8 +9471,11 @@
       <c r="L200" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="201" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M200" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="201" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A201">
         <v>40490956</v>
       </c>
@@ -8909,8 +9512,11 @@
       <c r="L201" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="202" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M201" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="202" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A202">
         <v>40491011</v>
       </c>
@@ -8947,8 +9553,11 @@
       <c r="L202" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="203" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M202" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="203" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A203">
         <v>40491478</v>
       </c>
@@ -8985,8 +9594,11 @@
       <c r="L203" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="204" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M203" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="204" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A204">
         <v>40491529</v>
       </c>
@@ -9023,8 +9635,11 @@
       <c r="L204" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="205" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M204" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="205" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A205">
         <v>40491967</v>
       </c>
@@ -9061,8 +9676,11 @@
       <c r="L205" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="206" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M205" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="206" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A206">
         <v>40492025</v>
       </c>
@@ -9099,8 +9717,11 @@
       <c r="L206" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="207" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M206" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="207" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A207">
         <v>40492189</v>
       </c>
@@ -9137,8 +9758,11 @@
       <c r="L207" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="208" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M207" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="208" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A208">
         <v>40492453</v>
       </c>
@@ -9175,8 +9799,11 @@
       <c r="L208" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="209" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M208" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="209" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A209">
         <v>40493447</v>
       </c>
@@ -9213,8 +9840,11 @@
       <c r="L209" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="210" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M209" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="210" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A210">
         <v>40493451</v>
       </c>
@@ -9251,8 +9881,11 @@
       <c r="L210" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="211" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M210" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="211" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A211">
         <v>40493459</v>
       </c>
@@ -9289,8 +9922,11 @@
       <c r="L211" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="212" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M211" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="212" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A212">
         <v>40493487</v>
       </c>
@@ -9327,8 +9963,11 @@
       <c r="L212" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="213" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M212" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="213" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A213">
         <v>42538529</v>
       </c>
@@ -9365,8 +10004,11 @@
       <c r="L213" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="214" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M213" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="214" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A214">
         <v>42539157</v>
       </c>
@@ -9403,8 +10045,11 @@
       <c r="L214" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="215" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M214" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="215" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A215">
         <v>43020504</v>
       </c>
@@ -9441,8 +10086,11 @@
       <c r="L215" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="216" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M215" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="216" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A216">
         <v>43020626</v>
       </c>
@@ -9479,8 +10127,11 @@
       <c r="L216" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="217" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M216" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="217" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A217">
         <v>43020627</v>
       </c>
@@ -9517,8 +10168,11 @@
       <c r="L217" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="218" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M217" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="218" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A218">
         <v>43020628</v>
       </c>
@@ -9555,8 +10209,11 @@
       <c r="L218" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="219" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M218" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="219" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A219">
         <v>43020629</v>
       </c>
@@ -9593,8 +10250,11 @@
       <c r="L219" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="220" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M219" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="220" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A220">
         <v>43020630</v>
       </c>
@@ -9631,8 +10291,11 @@
       <c r="L220" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="221" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M220" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="221" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A221">
         <v>43020882</v>
       </c>
@@ -9669,8 +10332,11 @@
       <c r="L221" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="222" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M221" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="222" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A222">
         <v>43020903</v>
       </c>
@@ -9707,8 +10373,11 @@
       <c r="L222" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="223" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M222" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="223" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A223">
         <v>43020913</v>
       </c>
@@ -9745,8 +10414,11 @@
       <c r="L223" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="224" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M223" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="224" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A224">
         <v>43020914</v>
       </c>
@@ -9783,8 +10455,11 @@
       <c r="L224" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="225" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M224" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="225" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A225">
         <v>43020915</v>
       </c>
@@ -9821,8 +10496,11 @@
       <c r="L225" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="226" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M225" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="226" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A226">
         <v>43020916</v>
       </c>
@@ -9859,8 +10537,11 @@
       <c r="L226" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="227" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M226" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="227" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A227">
         <v>43020917</v>
       </c>
@@ -9897,8 +10578,11 @@
       <c r="L227" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="228" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M227" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="228" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A228">
         <v>43020957</v>
       </c>
@@ -9935,8 +10619,11 @@
       <c r="L228" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="229" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M228" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="229" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A229">
         <v>43020959</v>
       </c>
@@ -9973,8 +10660,11 @@
       <c r="L229" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="230" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M229" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="230" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A230">
         <v>43020960</v>
       </c>
@@ -10011,8 +10701,11 @@
       <c r="L230" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="231" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M230" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="231" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A231">
         <v>43020962</v>
       </c>
@@ -10049,8 +10742,11 @@
       <c r="L231" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="232" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M231" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="232" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A232">
         <v>43020964</v>
       </c>
@@ -10087,8 +10783,11 @@
       <c r="L232" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="233" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M232" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="233" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A233">
         <v>43021070</v>
       </c>
@@ -10125,8 +10824,11 @@
       <c r="L233" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="234" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M233" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="234" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A234">
         <v>43021708</v>
       </c>
@@ -10163,8 +10865,11 @@
       <c r="L234" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="235" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M234" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="235" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A235">
         <v>43021806</v>
       </c>
@@ -10201,8 +10906,11 @@
       <c r="L235" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="236" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M235" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="236" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A236">
         <v>43021943</v>
       </c>
@@ -10239,8 +10947,11 @@
       <c r="L236" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="237" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M236" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="237" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A237">
         <v>43021944</v>
       </c>
@@ -10277,8 +10988,11 @@
       <c r="L237" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="238" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M237" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="238" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A238">
         <v>43021945</v>
       </c>
@@ -10315,8 +11029,11 @@
       <c r="L238" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="239" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M238" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="239" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A239">
         <v>45757096</v>
       </c>
@@ -10353,8 +11070,11 @@
       <c r="L239" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="240" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M239" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="240" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A240">
         <v>45766079</v>
       </c>
@@ -10391,8 +11111,11 @@
       <c r="L240" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="241" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M240" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="241" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A241">
         <v>45766080</v>
       </c>
@@ -10429,8 +11152,11 @@
       <c r="L241" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="242" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M241" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="242" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A242">
         <v>45766081</v>
       </c>
@@ -10467,8 +11193,11 @@
       <c r="L242" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="243" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M242" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="243" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A243">
         <v>45766082</v>
       </c>
@@ -10505,8 +11234,11 @@
       <c r="L243" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="244" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M243" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="244" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A244">
         <v>45766083</v>
       </c>
@@ -10543,8 +11275,11 @@
       <c r="L244" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="245" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M244" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="245" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A245">
         <v>45766084</v>
       </c>
@@ -10581,8 +11316,11 @@
       <c r="L245" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="246" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M245" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="246" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A246">
         <v>45766087</v>
       </c>
@@ -10619,8 +11357,11 @@
       <c r="L246" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="247" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M246" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="247" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A247">
         <v>45766089</v>
       </c>
@@ -10657,8 +11398,11 @@
       <c r="L247" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="248" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M247" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="248" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A248">
         <v>45766092</v>
       </c>
@@ -10695,8 +11439,11 @@
       <c r="L248" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="249" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M248" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="249" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A249">
         <v>45766095</v>
       </c>
@@ -10733,8 +11480,11 @@
       <c r="L249" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="250" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M249" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="250" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A250">
         <v>45766099</v>
       </c>
@@ -10771,8 +11521,11 @@
       <c r="L250" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="251" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M250" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="251" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A251">
         <v>45766124</v>
       </c>
@@ -10809,8 +11562,11 @@
       <c r="L251" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="252" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M251" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="252" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A252">
         <v>45766125</v>
       </c>
@@ -10847,8 +11603,11 @@
       <c r="L252" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="253" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M252" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="253" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A253">
         <v>45766126</v>
       </c>
@@ -10885,8 +11644,11 @@
       <c r="L253" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="254" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M253" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="254" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A254">
         <v>45766136</v>
       </c>
@@ -10923,8 +11685,11 @@
       <c r="L254" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="255" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M254" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="255" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A255">
         <v>45766181</v>
       </c>
@@ -10961,8 +11726,11 @@
       <c r="L255" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="256" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M255" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="256" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A256">
         <v>45766182</v>
       </c>
@@ -10999,8 +11767,11 @@
       <c r="L256" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="257" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M256" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="257" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A257">
         <v>45766185</v>
       </c>
@@ -11037,8 +11808,11 @@
       <c r="L257" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="258" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M257" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="258" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A258">
         <v>45766186</v>
       </c>
@@ -11075,8 +11849,11 @@
       <c r="L258" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="259" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M258" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="259" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A259">
         <v>45766205</v>
       </c>
@@ -11113,8 +11890,11 @@
       <c r="L259" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="260" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M259" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="260" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A260">
         <v>45766206</v>
       </c>
@@ -11151,8 +11931,11 @@
       <c r="L260" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="261" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M260" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="261" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A261">
         <v>45766207</v>
       </c>
@@ -11189,8 +11972,11 @@
       <c r="L261" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="262" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M261" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="262" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A262">
         <v>45766210</v>
       </c>
@@ -11227,8 +12013,11 @@
       <c r="L262" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="263" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M262" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="263" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A263">
         <v>45766211</v>
       </c>
@@ -11265,8 +12054,11 @@
       <c r="L263" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="264" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M263" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="264" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A264">
         <v>45766213</v>
       </c>
@@ -11303,8 +12095,11 @@
       <c r="L264" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="265" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M264" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="265" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A265">
         <v>45766214</v>
       </c>
@@ -11341,8 +12136,11 @@
       <c r="L265" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="266" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M265" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="266" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A266">
         <v>45771317</v>
       </c>
@@ -11379,8 +12177,11 @@
       <c r="L266" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="267" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M266" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="267" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A267">
         <v>45771321</v>
       </c>
@@ -11417,8 +12218,11 @@
       <c r="L267" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="268" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M267" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="268" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A268">
         <v>45771323</v>
       </c>
@@ -11455,8 +12259,11 @@
       <c r="L268" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="269" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M268" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="269" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A269">
         <v>45771326</v>
       </c>
@@ -11493,8 +12300,11 @@
       <c r="L269" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="270" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M269" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="270" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A270">
         <v>45771327</v>
       </c>
@@ -11531,8 +12341,11 @@
       <c r="L270" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="271" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M270" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="271" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A271">
         <v>45773080</v>
       </c>
@@ -11567,6 +12380,9 @@
         <v>14</v>
       </c>
       <c r="L271" t="s">
+        <v>14</v>
+      </c>
+      <c r="M271" t="s">
         <v>14</v>
       </c>
     </row>
